--- a/PerformanceReports/GET_PERFORMANCE_API_REPORT.xlsx
+++ b/PerformanceReports/GET_PERFORMANCE_API_REPORT.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="246">
   <si>
     <t xml:space="preserve">Run Number</t>
   </si>
@@ -456,6 +456,15 @@
     <t xml:space="preserve">10:49:19</t>
   </si>
   <si>
+    <t xml:space="preserve">Sprint_217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:47:48</t>
+  </si>
+  <si>
     <t xml:space="preserve">11:53:AM</t>
   </si>
   <si>
@@ -513,6 +522,9 @@
     <t xml:space="preserve">10:50:56</t>
   </si>
   <si>
+    <t xml:space="preserve">11:10:38</t>
+  </si>
+  <si>
     <t xml:space="preserve">14:25:00</t>
   </si>
   <si>
@@ -567,6 +579,9 @@
     <t xml:space="preserve">15:09:47</t>
   </si>
   <si>
+    <t xml:space="preserve">16:22:04</t>
+  </si>
+  <si>
     <t xml:space="preserve">14:27:23</t>
   </si>
   <si>
@@ -616,6 +631,9 @@
   </si>
   <si>
     <t xml:space="preserve">15:08:32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:21:34</t>
   </si>
   <si>
     <t xml:space="preserve">11:21:AM</t>
@@ -684,6 +702,9 @@
     <t xml:space="preserve">11:39:59</t>
   </si>
   <si>
+    <t xml:space="preserve">20:51:54</t>
+  </si>
+  <si>
     <t xml:space="preserve">11:17:AM</t>
   </si>
   <si>
@@ -739,6 +760,9 @@
   </si>
   <si>
     <t xml:space="preserve">11:39:55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:52:10</t>
   </si>
 </sst>
 </file>
@@ -854,7 +878,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -880,6 +904,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1157,7 +1185,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="21.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="21.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="29.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="26.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="26.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="31.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="34.54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="18.96"/>
@@ -1175,12 +1203,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="20.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="14.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="29.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="23.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="23.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="16.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="1" width="31.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="1" width="21.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="43" style="1" width="13.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="29.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="29.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="45" style="1" width="22.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="46" style="1" width="15.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="47" style="1" width="31.06"/>
@@ -1203,11 +1231,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="1" width="12.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="65" min="65" style="1" width="31.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="66" min="66" style="1" width="20.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="67" min="67" style="1" width="10.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="67" min="67" style="1" width="10.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="68" min="68" style="1" width="28.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="69" min="69" style="1" width="21.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="70" min="70" style="1" width="10.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="71" min="71" style="1" width="29.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="70" min="70" style="1" width="10.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="71" min="71" style="1" width="29.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="72" min="72" style="1" width="22.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="73" min="73" style="1" width="12.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="74" min="74" style="1" width="31.9"/>
@@ -5500,6 +5528,264 @@
       <c r="CE21" s="1" t="n">
         <v>-59.09</v>
       </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="I22" s="1" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J22" s="1" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K22" s="1" t="n">
+        <v>-11.11</v>
+      </c>
+      <c r="L22" s="1" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M22" s="1" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N22" s="1" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="O22" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P22" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q22" s="1" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R22" s="1" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="S22" s="1" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="T22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="1" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="V22" s="1" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="W22" s="1" t="n">
+        <v>-8.11</v>
+      </c>
+      <c r="X22" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y22" s="1" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="Z22" s="1" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="AA22" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB22" s="1" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AC22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="1" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AE22" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AF22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH22" s="1" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AI22" s="1" t="n">
+        <v>-4.17</v>
+      </c>
+      <c r="AJ22" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK22" s="1" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AL22" s="1" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AM22" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN22" s="1" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AO22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ22" s="1" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AR22" s="1" t="n">
+        <v>-4.55</v>
+      </c>
+      <c r="AS22" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AT22" s="1" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AU22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" s="1" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AW22" s="1" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AX22" s="1" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="AY22" s="1" t="n">
+        <v>0.81</v>
+      </c>
+      <c r="AZ22" s="1" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="BA22" s="1" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="BB22" s="1" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BC22" s="1" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BD22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" s="1" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BF22" s="1" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BG22" s="1" t="n">
+        <v>-5.26</v>
+      </c>
+      <c r="BH22" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI22" s="5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BJ22" s="1" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="BK22" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BL22" s="1" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BM22" s="1" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BN22" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BO22" s="5" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="BP22" s="1" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="BQ22" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BR22" s="1" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BS22" s="1" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="BT22" s="1" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="BU22" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BV22" s="1" t="n">
+        <v>-9.09</v>
+      </c>
+      <c r="BW22" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BX22" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BY22" s="1" t="n">
+        <v>-10</v>
+      </c>
+      <c r="BZ22" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CA22" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="CB22" s="5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="CC22" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="CD22" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="CE22" s="5" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="BI23" s="5"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="BI24" s="5"/>
+      <c r="BY24" s="5"/>
     </row>
     <row r="1048547" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048548" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -5551,7 +5837,7 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.62"/>
@@ -5569,7 +5855,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="21.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="21.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="29.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="26.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="26.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="31.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="34.54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="18.96"/>
@@ -5587,12 +5873,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="20.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="14.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="29.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="23.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="23.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="16.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="1" width="31.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="1" width="21.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="43" style="1" width="13.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="29.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="29.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="45" style="1" width="22.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="46" style="1" width="15.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="47" style="1" width="31.06"/>
@@ -5615,11 +5901,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="1" width="12.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="65" min="65" style="1" width="31.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="66" min="66" style="1" width="20.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="67" min="67" style="1" width="10.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="67" min="67" style="1" width="10.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="68" min="68" style="1" width="28.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="69" min="69" style="1" width="21.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="70" min="70" style="1" width="10.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="71" min="71" style="1" width="29.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="70" min="70" style="1" width="10.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="71" min="71" style="1" width="29.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="72" min="72" style="1" width="22.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="73" min="73" style="1" width="12.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="74" min="74" style="1" width="31.9"/>
@@ -5896,7 +6182,7 @@
         <v>84</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>15</v>
@@ -5943,7 +6229,7 @@
         <v>87</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>15</v>
@@ -6005,7 +6291,7 @@
         <v>90</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>15</v>
@@ -6067,7 +6353,7 @@
         <v>93</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>15</v>
@@ -6207,7 +6493,7 @@
         <v>96</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>15</v>
@@ -6374,7 +6660,7 @@
         <v>102</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>30</v>
@@ -6541,7 +6827,7 @@
         <v>105</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>30</v>
@@ -6708,7 +6994,7 @@
         <v>108</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>50</v>
@@ -6875,7 +7161,7 @@
         <v>111</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>100</v>
@@ -7090,7 +7376,7 @@
         <v>114</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>100</v>
@@ -7305,7 +7591,7 @@
         <v>117</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>100</v>
@@ -7520,7 +7806,7 @@
         <v>120</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>100</v>
@@ -7735,7 +8021,7 @@
         <v>123</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>100</v>
@@ -7950,7 +8236,7 @@
         <v>126</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>100</v>
@@ -8165,7 +8451,7 @@
         <v>129</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>100</v>
@@ -8380,7 +8666,7 @@
         <v>132</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>100</v>
@@ -8595,7 +8881,7 @@
         <v>135</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>100</v>
@@ -8810,7 +9096,7 @@
         <v>138</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>100</v>
@@ -9025,7 +9311,7 @@
         <v>141</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E20" s="1" t="n">
         <v>100</v>
@@ -9226,6 +9512,221 @@
         <v>0</v>
       </c>
       <c r="CD20" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G21" s="1" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="I21" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J21" s="1" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K21" s="1" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="L21" s="1" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="M21" s="1" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="N21" s="1" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="O21" s="1" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="P21" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q21" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="R21" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S21" s="1" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="T21" s="1" t="n">
+        <v>-25.49</v>
+      </c>
+      <c r="U21" s="1" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V21" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W21" s="1" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X21" s="1" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y21" s="1" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Z21" s="5" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="AA21" s="1" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB21" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC21" s="5" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="AD21" s="1" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE21" s="1" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AF21" s="1" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AG21" s="1" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH21" s="1" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AI21" s="1" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="AJ21" s="1" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK21" s="1" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AL21" s="1" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="AM21" s="1" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN21" s="1" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AO21" s="5" t="n">
+        <v>20.59</v>
+      </c>
+      <c r="AP21" s="1" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ21" s="1" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AR21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" s="1" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT21" s="1" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AU21" s="1" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="AV21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD21" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9255,7 +9756,7 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.62"/>
@@ -9273,7 +9774,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="21.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="21.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="29.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="26.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="26.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="31.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="34.54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="18.96"/>
@@ -9291,12 +9792,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="20.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="14.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="29.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="23.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="23.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="16.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="1" width="31.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="1" width="21.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="43" style="1" width="13.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="29.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="29.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="45" style="1" width="22.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="46" style="1" width="15.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="47" style="1" width="31.06"/>
@@ -9319,11 +9820,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="1" width="12.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="65" min="65" style="1" width="31.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="66" min="66" style="1" width="20.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="67" min="67" style="1" width="10.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="67" min="67" style="1" width="10.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="68" min="68" style="1" width="28.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="69" min="69" style="1" width="21.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="70" min="70" style="1" width="10.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="71" min="71" style="1" width="29.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="70" min="70" style="1" width="10.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="71" min="71" style="1" width="29.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="72" min="72" style="1" width="22.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="73" min="73" style="1" width="12.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="74" min="74" style="1" width="31.9"/>
@@ -9600,7 +10101,7 @@
         <v>90</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>15</v>
@@ -9647,7 +10148,7 @@
         <v>93</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>15</v>
@@ -9787,7 +10288,7 @@
         <v>96</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>15</v>
@@ -9966,7 +10467,7 @@
         <v>102</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>30</v>
@@ -10145,7 +10646,7 @@
         <v>105</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>30</v>
@@ -10324,7 +10825,7 @@
         <v>108</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>50</v>
@@ -10503,7 +11004,7 @@
         <v>111</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>100</v>
@@ -10706,7 +11207,7 @@
         <v>114</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>100</v>
@@ -10949,7 +11450,7 @@
         <v>117</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>100</v>
@@ -11200,7 +11701,7 @@
         <v>120</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>100</v>
@@ -11451,7 +11952,7 @@
         <v>123</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>100</v>
@@ -11702,7 +12203,7 @@
         <v>126</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>100</v>
@@ -11953,7 +12454,7 @@
         <v>129</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>5</v>
@@ -12204,7 +12705,7 @@
         <v>129</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>100</v>
@@ -12455,7 +12956,7 @@
         <v>132</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>100</v>
@@ -12706,7 +13207,7 @@
         <v>135</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>100</v>
@@ -12957,7 +13458,7 @@
         <v>138</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>100</v>
@@ -13208,7 +13709,7 @@
         <v>141</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>100</v>
@@ -13445,6 +13946,257 @@
         <v>0.14</v>
       </c>
       <c r="CE19" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="I20" s="1" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J20" s="1" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="K20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="1" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M20" s="1" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P20" s="1" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q20" s="1" t="n">
+        <v>-12</v>
+      </c>
+      <c r="R20" s="1" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="S20" s="1" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="T20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V20" s="1" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="W20" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X20" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y20" s="1" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="Z20" s="1" t="n">
+        <v>-5.56</v>
+      </c>
+      <c r="AA20" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB20" s="1" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AC20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE20" s="1" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AF20" s="1" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="AG20" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH20" s="1" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AI20" s="1" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="AJ20" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK20" s="1" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AL20" s="1" t="n">
+        <v>-6.25</v>
+      </c>
+      <c r="AM20" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN20" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AO20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ20" s="1" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AR20" s="1" t="n">
+        <v>-4.55</v>
+      </c>
+      <c r="AS20" s="1" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AT20" s="1" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AU20" s="1" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV20" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AW20" s="1" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AX20" s="1" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY20" s="1" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AZ20" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BA20" s="1" t="n">
+        <v>-5.41</v>
+      </c>
+      <c r="BB20" s="1" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BC20" s="1" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BD20" s="1" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="BE20" s="1" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BF20" s="1" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BG20" s="1" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="BH20" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BI20" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BJ20" s="1" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="BK20" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL20" s="1" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BM20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN20" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BO20" s="1" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="BP20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ20" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BR20" s="1" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BS20" s="1" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="BT20" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BU20" s="1" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BV20" s="1" t="n">
+        <v>-6.9</v>
+      </c>
+      <c r="BW20" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BX20" s="1" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BY20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA20" s="1" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="CB20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC20" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CD20" s="1" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="CE20" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13469,7 +14221,7 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.62"/>
@@ -13487,7 +14239,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="21.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="21.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="29.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="26.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="26.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="31.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="34.54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="18.96"/>
@@ -13505,12 +14257,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="20.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="14.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="29.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="23.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="23.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="16.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="1" width="31.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="1" width="21.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="43" style="1" width="13.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="29.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="29.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="45" style="1" width="22.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="46" style="1" width="15.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="47" style="1" width="31.06"/>
@@ -13533,11 +14285,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="1" width="12.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="65" min="65" style="1" width="31.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="66" min="66" style="1" width="20.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="67" min="67" style="1" width="10.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="67" min="67" style="1" width="10.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="68" min="68" style="1" width="28.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="69" min="69" style="1" width="21.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="70" min="70" style="1" width="10.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="71" min="71" style="1" width="29.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="70" min="70" style="1" width="10.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="71" min="71" style="1" width="29.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="72" min="72" style="1" width="22.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="73" min="73" style="1" width="12.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="74" min="74" style="1" width="31.9"/>
@@ -13814,7 +14566,7 @@
         <v>90</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>15</v>
@@ -13861,7 +14613,7 @@
         <v>93</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>15</v>
@@ -14001,7 +14753,7 @@
         <v>96</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>15</v>
@@ -14168,7 +14920,7 @@
         <v>102</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>30</v>
@@ -14335,7 +15087,7 @@
         <v>105</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>30</v>
@@ -14502,7 +15254,7 @@
         <v>108</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>50</v>
@@ -14669,7 +15421,7 @@
         <v>111</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>100</v>
@@ -14884,7 +15636,7 @@
         <v>114</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>100</v>
@@ -15099,7 +15851,7 @@
         <v>117</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>100</v>
@@ -15314,7 +16066,7 @@
         <v>120</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>100</v>
@@ -15529,7 +16281,7 @@
         <v>123</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>100</v>
@@ -15744,7 +16496,7 @@
         <v>126</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>100</v>
@@ -15959,7 +16711,7 @@
         <v>129</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>100</v>
@@ -16174,7 +16926,7 @@
         <v>132</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>100</v>
@@ -16389,7 +17141,7 @@
         <v>135</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>100</v>
@@ -16604,7 +17356,7 @@
         <v>138</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>100</v>
@@ -16819,7 +17571,7 @@
         <v>141</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>100</v>
@@ -17020,6 +17772,221 @@
         <v>0</v>
       </c>
       <c r="CD18" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="I19" s="1" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="J19" s="1" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>-6.52</v>
+      </c>
+      <c r="L19" s="1" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="M19" s="1" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="N19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P19" s="1" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q19" s="7" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="R19" s="1" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="S19" s="1" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="T19" s="1" t="n">
+        <v>-12.73</v>
+      </c>
+      <c r="U19" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V19" s="1" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="W19" s="1" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="X19" s="1" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Y19" s="1" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z19" s="1" t="n">
+        <v>-19.51</v>
+      </c>
+      <c r="AA19" s="1" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB19" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AC19" s="1" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="AD19" s="1" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE19" s="1" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AF19" s="1" t="n">
+        <v>-6.67</v>
+      </c>
+      <c r="AG19" s="1" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH19" s="1" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AI19" s="1" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AJ19" s="1" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AK19" s="1" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AL19" s="1" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AM19" s="1" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN19" s="1" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AO19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" s="1" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ19" s="1" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AR19" s="1" t="n">
+        <v>-14.58</v>
+      </c>
+      <c r="AS19" s="1" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AT19" s="1" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AU19" s="1" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AV19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD19" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17062,7 +18029,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="21.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="21.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="29.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="26.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="26.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="31.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="34.54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="18.96"/>
@@ -17080,12 +18047,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="20.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="14.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="29.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="23.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="23.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="16.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="1" width="31.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="1" width="21.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="43" style="1" width="13.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="29.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="29.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="45" style="1" width="22.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="46" style="1" width="15.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="47" style="1" width="31.06"/>
@@ -17108,11 +18075,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="1" width="12.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="65" min="65" style="1" width="31.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="66" min="66" style="1" width="20.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="67" min="67" style="1" width="10.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="67" min="67" style="1" width="10.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="68" min="68" style="1" width="28.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="69" min="69" style="1" width="21.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="70" min="70" style="1" width="10.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="71" min="71" style="1" width="29.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="70" min="70" style="1" width="10.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="71" min="71" style="1" width="29.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="72" min="72" style="1" width="22.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="73" min="73" style="1" width="12.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="74" min="74" style="1" width="31.9"/>
@@ -17389,7 +18356,7 @@
         <v>84</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>15</v>
@@ -17436,7 +18403,7 @@
         <v>87</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>15</v>
@@ -17498,7 +18465,7 @@
         <v>90</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>15</v>
@@ -17560,7 +18527,7 @@
         <v>93</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>15</v>
@@ -17700,7 +18667,7 @@
         <v>96</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>15</v>
@@ -17879,7 +18846,7 @@
         <v>102</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>30</v>
@@ -18058,7 +19025,7 @@
         <v>105</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>30</v>
@@ -18237,7 +19204,7 @@
         <v>108</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>50</v>
@@ -18416,7 +19383,7 @@
         <v>111</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>100</v>
@@ -18625,7 +19592,7 @@
         <v>114</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>100</v>
@@ -18835,7 +19802,7 @@
         <v>0.29</v>
       </c>
       <c r="BV11" s="5" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="BW11" s="1" t="n">
         <v>0.8</v>
@@ -18867,10 +19834,10 @@
         <v>116</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>100</v>
@@ -19121,7 +20088,7 @@
         <v>120</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>100</v>
@@ -19372,7 +20339,7 @@
         <v>123</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>100</v>
@@ -19623,7 +20590,7 @@
         <v>126</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>100</v>
@@ -19874,7 +20841,7 @@
         <v>129</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>100</v>
@@ -20125,7 +21092,7 @@
         <v>132</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>100</v>
@@ -20376,7 +21343,7 @@
         <v>135</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>100</v>
@@ -20627,7 +21594,7 @@
         <v>138</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>100</v>
@@ -20867,7 +21834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
@@ -20875,10 +21842,10 @@
         <v>140</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="E20" s="1" t="n">
         <v>100</v>
@@ -21116,6 +22083,257 @@
       </c>
       <c r="CE20" s="1" t="n">
         <v>-6.67</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="G21" s="1" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="I21" s="1" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J21" s="1" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K21" s="1" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="L21" s="1" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M21" s="1" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="N21" s="1" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O21" s="1" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="P21" s="1" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="Q21" s="1" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R21" s="1" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="S21" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T21" s="1" t="n">
+        <v>-2.78</v>
+      </c>
+      <c r="U21" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V21" s="1" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="W21" s="1" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="X21" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y21" s="1" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="Z21" s="1" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="AA21" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB21" s="1" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AC21" s="1" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AD21" s="1" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AE21" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AF21" s="1" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG21" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH21" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AI21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK21" s="1" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AL21" s="1" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AM21" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN21" s="1" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AO21" s="1" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="AP21" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ21" s="1" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AR21" s="1" t="n">
+        <v>-4.55</v>
+      </c>
+      <c r="AS21" s="1" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AT21" s="1" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AU21" s="1" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV21" s="1" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AW21" s="1" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AX21" s="1" t="n">
+        <v>-2.94</v>
+      </c>
+      <c r="AY21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ21" s="1" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="BA21" s="1" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="BB21" s="1" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="BC21" s="1" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BD21" s="1" t="n">
+        <v>-4.08</v>
+      </c>
+      <c r="BE21" s="1" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BF21" s="1" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BG21" s="1" t="n">
+        <v>-3.03</v>
+      </c>
+      <c r="BH21" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BI21" s="1" t="n">
+        <v>0.81</v>
+      </c>
+      <c r="BJ21" s="1" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="BK21" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL21" s="1" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BM21" s="1" t="n">
+        <v>-6.9</v>
+      </c>
+      <c r="BN21" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BO21" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BP21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ21" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BR21" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BS21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT21" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BU21" s="1" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BV21" s="1" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="BW21" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BX21" s="1" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="BY21" s="1" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="BZ21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA21" s="1" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="CB21" s="1" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="CC21" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CD21" s="1" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="CE21" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1048569" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -21146,7 +22364,7 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.62"/>
@@ -21164,7 +22382,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="21.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="21.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="29.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="26.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="26.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="31.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="34.54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="18.96"/>
@@ -21182,12 +22400,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="20.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="14.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="29.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="23.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="23.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="16.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="1" width="31.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="1" width="21.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="43" style="1" width="13.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="29.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="29.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="45" style="1" width="22.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="46" style="1" width="15.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="47" style="1" width="31.06"/>
@@ -21210,11 +22428,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="1" width="12.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="65" min="65" style="1" width="31.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="66" min="66" style="1" width="20.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="67" min="67" style="1" width="10.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="67" min="67" style="1" width="10.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="68" min="68" style="1" width="28.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="69" min="69" style="1" width="21.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="70" min="70" style="1" width="10.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="71" min="71" style="1" width="29.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="70" min="70" style="1" width="10.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="71" min="71" style="1" width="29.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="72" min="72" style="1" width="22.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="73" min="73" style="1" width="12.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="74" min="74" style="1" width="31.9"/>
@@ -21491,7 +22709,7 @@
         <v>84</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>15</v>
@@ -21538,7 +22756,7 @@
         <v>87</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>15</v>
@@ -21600,7 +22818,7 @@
         <v>90</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>15</v>
@@ -21662,7 +22880,7 @@
         <v>93</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>15</v>
@@ -21802,7 +23020,7 @@
         <v>96</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>15</v>
@@ -21969,7 +23187,7 @@
         <v>102</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>30</v>
@@ -22136,7 +23354,7 @@
         <v>105</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>30</v>
@@ -22303,7 +23521,7 @@
         <v>108</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>50</v>
@@ -22470,7 +23688,7 @@
         <v>111</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>100</v>
@@ -22685,7 +23903,7 @@
         <v>114</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>100</v>
@@ -22897,10 +24115,10 @@
         <v>116</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>100</v>
@@ -23115,7 +24333,7 @@
         <v>120</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>100</v>
@@ -23330,7 +24548,7 @@
         <v>123</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>100</v>
@@ -23545,7 +24763,7 @@
         <v>126</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>100</v>
@@ -23760,7 +24978,7 @@
         <v>129</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>100</v>
@@ -23975,7 +25193,7 @@
         <v>132</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>100</v>
@@ -24190,7 +25408,7 @@
         <v>135</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>100</v>
@@ -24405,7 +25623,7 @@
         <v>138</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>100</v>
@@ -24609,7 +25827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
@@ -24617,10 +25835,10 @@
         <v>140</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E20" s="1" t="n">
         <v>100</v>
@@ -24821,6 +26039,221 @@
         <v>0</v>
       </c>
       <c r="CD20" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G21" s="1" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>-2.86</v>
+      </c>
+      <c r="I21" s="1" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="J21" s="1" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="K21" s="1" t="n">
+        <v>-11.9</v>
+      </c>
+      <c r="L21" s="1" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="M21" s="1" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="N21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="1" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="P21" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Q21" s="1" t="n">
+        <v>-10.26</v>
+      </c>
+      <c r="R21" s="1" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S21" s="1" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="T21" s="1" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="U21" s="1" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V21" s="1" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="W21" s="1" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="X21" s="1" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Y21" s="1" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="1" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB21" s="1" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AC21" s="1" t="n">
+        <v>-3.03</v>
+      </c>
+      <c r="AD21" s="1" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE21" s="1" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AF21" s="1" t="n">
+        <v>-6.52</v>
+      </c>
+      <c r="AG21" s="1" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH21" s="1" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AI21" s="1" t="n">
+        <v>-2.63</v>
+      </c>
+      <c r="AJ21" s="1" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AK21" s="1" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AL21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" s="1" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN21" s="1" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AO21" s="1" t="n">
+        <v>-7.69</v>
+      </c>
+      <c r="AP21" s="1" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ21" s="1" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AR21" s="1" t="n">
+        <v>-9.3</v>
+      </c>
+      <c r="AS21" s="1" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AT21" s="1" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AU21" s="1" t="n">
+        <v>-4.88</v>
+      </c>
+      <c r="AV21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD21" s="1" t="n">
         <v>0</v>
       </c>
     </row>

--- a/PerformanceReports/GET_PERFORMANCE_API_REPORT.xlsx
+++ b/PerformanceReports/GET_PERFORMANCE_API_REPORT.xlsx
@@ -963,98 +963,98 @@
       <c r="G2" s="8" t="n">
         <v>0.44</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" s="8" t="inlineStr"/>
       <c r="I2" s="8" t="n">
         <v>0.48</v>
       </c>
       <c r="J2" s="8" t="n">
         <v>0.42</v>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" s="8" t="inlineStr"/>
       <c r="L2" s="8" t="n">
         <v>0.53</v>
       </c>
       <c r="M2" s="8" t="n">
         <v>0.46</v>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" s="8" t="inlineStr"/>
       <c r="O2" s="8" t="n">
         <v>0.75</v>
       </c>
       <c r="P2" s="8" t="n">
         <v>0.67</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
+      <c r="Q2" s="8" t="inlineStr"/>
       <c r="R2" s="8" t="n">
         <v>0.44</v>
       </c>
       <c r="S2" s="8" t="n">
         <v>0.4</v>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr"/>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="inlineStr"/>
-      <c r="BR2" t="inlineStr"/>
-      <c r="BS2" t="inlineStr"/>
-      <c r="BT2" t="inlineStr"/>
-      <c r="BU2" t="inlineStr"/>
-      <c r="BV2" t="inlineStr"/>
-      <c r="BW2" t="inlineStr"/>
-      <c r="BX2" t="inlineStr"/>
-      <c r="BY2" t="inlineStr"/>
-      <c r="BZ2" t="inlineStr"/>
-      <c r="CA2" t="inlineStr"/>
-      <c r="CB2" t="inlineStr"/>
-      <c r="CC2" t="inlineStr"/>
-      <c r="CD2" t="inlineStr"/>
-      <c r="CE2" t="inlineStr"/>
+      <c r="T2" s="8" t="inlineStr"/>
+      <c r="U2" s="8" t="inlineStr"/>
+      <c r="V2" s="8" t="inlineStr"/>
+      <c r="W2" s="8" t="inlineStr"/>
+      <c r="X2" s="8" t="inlineStr"/>
+      <c r="Y2" s="8" t="inlineStr"/>
+      <c r="Z2" s="8" t="inlineStr"/>
+      <c r="AA2" s="8" t="inlineStr"/>
+      <c r="AB2" s="8" t="inlineStr"/>
+      <c r="AC2" s="8" t="inlineStr"/>
+      <c r="AD2" s="8" t="inlineStr"/>
+      <c r="AE2" s="8" t="inlineStr"/>
+      <c r="AF2" s="8" t="inlineStr"/>
+      <c r="AG2" s="8" t="inlineStr"/>
+      <c r="AH2" s="8" t="inlineStr"/>
+      <c r="AI2" s="8" t="inlineStr"/>
+      <c r="AJ2" s="8" t="inlineStr"/>
+      <c r="AK2" s="8" t="inlineStr"/>
+      <c r="AL2" s="8" t="inlineStr"/>
+      <c r="AM2" s="8" t="inlineStr"/>
+      <c r="AN2" s="8" t="inlineStr"/>
+      <c r="AO2" s="8" t="inlineStr"/>
+      <c r="AP2" s="8" t="inlineStr"/>
+      <c r="AQ2" s="8" t="inlineStr"/>
+      <c r="AR2" s="8" t="inlineStr"/>
+      <c r="AS2" s="8" t="inlineStr"/>
+      <c r="AT2" s="8" t="inlineStr"/>
+      <c r="AU2" s="8" t="inlineStr"/>
+      <c r="AV2" s="8" t="inlineStr"/>
+      <c r="AW2" s="8" t="inlineStr"/>
+      <c r="AX2" s="8" t="inlineStr"/>
+      <c r="AY2" s="8" t="inlineStr"/>
+      <c r="AZ2" s="8" t="inlineStr"/>
+      <c r="BA2" s="8" t="inlineStr"/>
+      <c r="BB2" s="8" t="inlineStr"/>
+      <c r="BC2" s="8" t="inlineStr"/>
+      <c r="BD2" s="8" t="inlineStr"/>
+      <c r="BE2" s="8" t="inlineStr"/>
+      <c r="BF2" s="8" t="inlineStr"/>
+      <c r="BG2" s="8" t="inlineStr"/>
+      <c r="BH2" s="8" t="inlineStr"/>
+      <c r="BI2" s="8" t="inlineStr"/>
+      <c r="BJ2" s="8" t="inlineStr"/>
+      <c r="BK2" s="8" t="inlineStr"/>
+      <c r="BL2" s="8" t="inlineStr"/>
+      <c r="BM2" s="8" t="inlineStr"/>
+      <c r="BN2" s="8" t="inlineStr"/>
+      <c r="BO2" s="8" t="inlineStr"/>
+      <c r="BP2" s="8" t="inlineStr"/>
+      <c r="BQ2" s="8" t="inlineStr"/>
+      <c r="BR2" s="8" t="inlineStr"/>
+      <c r="BS2" s="8" t="inlineStr"/>
+      <c r="BT2" s="8" t="inlineStr"/>
+      <c r="BU2" s="8" t="inlineStr"/>
+      <c r="BV2" s="8" t="inlineStr"/>
+      <c r="BW2" s="8" t="inlineStr"/>
+      <c r="BX2" s="8" t="inlineStr"/>
+      <c r="BY2" s="8" t="inlineStr"/>
+      <c r="BZ2" s="8" t="inlineStr"/>
+      <c r="CA2" s="8" t="inlineStr"/>
+      <c r="CB2" s="8" t="inlineStr"/>
+      <c r="CC2" s="8" t="inlineStr"/>
+      <c r="CD2" s="8" t="inlineStr"/>
+      <c r="CE2" s="8" t="inlineStr"/>
       <c r="XDC2" s="8" t="n"/>
       <c r="XDD2" s="8" t="n"/>
       <c r="XDE2" s="8" t="n"/>
@@ -1136,69 +1136,69 @@
       <c r="T3" s="8" t="n">
         <v>17.5</v>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="inlineStr"/>
-      <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="inlineStr"/>
-      <c r="BQ3" t="inlineStr"/>
-      <c r="BR3" t="inlineStr"/>
-      <c r="BS3" t="inlineStr"/>
-      <c r="BT3" t="inlineStr"/>
-      <c r="BU3" t="inlineStr"/>
-      <c r="BV3" t="inlineStr"/>
-      <c r="BW3" t="inlineStr"/>
-      <c r="BX3" t="inlineStr"/>
-      <c r="BY3" t="inlineStr"/>
-      <c r="BZ3" t="inlineStr"/>
-      <c r="CA3" t="inlineStr"/>
-      <c r="CB3" t="inlineStr"/>
-      <c r="CC3" t="inlineStr"/>
-      <c r="CD3" t="inlineStr"/>
-      <c r="CE3" t="inlineStr"/>
+      <c r="U3" s="8" t="inlineStr"/>
+      <c r="V3" s="8" t="inlineStr"/>
+      <c r="W3" s="8" t="inlineStr"/>
+      <c r="X3" s="8" t="inlineStr"/>
+      <c r="Y3" s="8" t="inlineStr"/>
+      <c r="Z3" s="8" t="inlineStr"/>
+      <c r="AA3" s="8" t="inlineStr"/>
+      <c r="AB3" s="8" t="inlineStr"/>
+      <c r="AC3" s="8" t="inlineStr"/>
+      <c r="AD3" s="8" t="inlineStr"/>
+      <c r="AE3" s="8" t="inlineStr"/>
+      <c r="AF3" s="8" t="inlineStr"/>
+      <c r="AG3" s="8" t="inlineStr"/>
+      <c r="AH3" s="8" t="inlineStr"/>
+      <c r="AI3" s="8" t="inlineStr"/>
+      <c r="AJ3" s="8" t="inlineStr"/>
+      <c r="AK3" s="8" t="inlineStr"/>
+      <c r="AL3" s="8" t="inlineStr"/>
+      <c r="AM3" s="8" t="inlineStr"/>
+      <c r="AN3" s="8" t="inlineStr"/>
+      <c r="AO3" s="8" t="inlineStr"/>
+      <c r="AP3" s="8" t="inlineStr"/>
+      <c r="AQ3" s="8" t="inlineStr"/>
+      <c r="AR3" s="8" t="inlineStr"/>
+      <c r="AS3" s="8" t="inlineStr"/>
+      <c r="AT3" s="8" t="inlineStr"/>
+      <c r="AU3" s="8" t="inlineStr"/>
+      <c r="AV3" s="8" t="inlineStr"/>
+      <c r="AW3" s="8" t="inlineStr"/>
+      <c r="AX3" s="8" t="inlineStr"/>
+      <c r="AY3" s="8" t="inlineStr"/>
+      <c r="AZ3" s="8" t="inlineStr"/>
+      <c r="BA3" s="8" t="inlineStr"/>
+      <c r="BB3" s="8" t="inlineStr"/>
+      <c r="BC3" s="8" t="inlineStr"/>
+      <c r="BD3" s="8" t="inlineStr"/>
+      <c r="BE3" s="8" t="inlineStr"/>
+      <c r="BF3" s="8" t="inlineStr"/>
+      <c r="BG3" s="8" t="inlineStr"/>
+      <c r="BH3" s="8" t="inlineStr"/>
+      <c r="BI3" s="8" t="inlineStr"/>
+      <c r="BJ3" s="8" t="inlineStr"/>
+      <c r="BK3" s="8" t="inlineStr"/>
+      <c r="BL3" s="8" t="inlineStr"/>
+      <c r="BM3" s="8" t="inlineStr"/>
+      <c r="BN3" s="8" t="inlineStr"/>
+      <c r="BO3" s="8" t="inlineStr"/>
+      <c r="BP3" s="8" t="inlineStr"/>
+      <c r="BQ3" s="8" t="inlineStr"/>
+      <c r="BR3" s="8" t="inlineStr"/>
+      <c r="BS3" s="8" t="inlineStr"/>
+      <c r="BT3" s="8" t="inlineStr"/>
+      <c r="BU3" s="8" t="inlineStr"/>
+      <c r="BV3" s="8" t="inlineStr"/>
+      <c r="BW3" s="8" t="inlineStr"/>
+      <c r="BX3" s="8" t="inlineStr"/>
+      <c r="BY3" s="8" t="inlineStr"/>
+      <c r="BZ3" s="8" t="inlineStr"/>
+      <c r="CA3" s="8" t="inlineStr"/>
+      <c r="CB3" s="8" t="inlineStr"/>
+      <c r="CC3" s="8" t="inlineStr"/>
+      <c r="CD3" s="8" t="inlineStr"/>
+      <c r="CE3" s="8" t="inlineStr"/>
       <c r="XDC3" s="8" t="n"/>
       <c r="XDD3" s="8" t="n"/>
       <c r="XDE3" s="8" t="n"/>
@@ -1280,69 +1280,69 @@
       <c r="T4" s="13" t="n">
         <v>46.81</v>
       </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
-      <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr"/>
-      <c r="BQ4" t="inlineStr"/>
-      <c r="BR4" t="inlineStr"/>
-      <c r="BS4" t="inlineStr"/>
-      <c r="BT4" t="inlineStr"/>
-      <c r="BU4" t="inlineStr"/>
-      <c r="BV4" t="inlineStr"/>
-      <c r="BW4" t="inlineStr"/>
-      <c r="BX4" t="inlineStr"/>
-      <c r="BY4" t="inlineStr"/>
-      <c r="BZ4" t="inlineStr"/>
-      <c r="CA4" t="inlineStr"/>
-      <c r="CB4" t="inlineStr"/>
-      <c r="CC4" t="inlineStr"/>
-      <c r="CD4" t="inlineStr"/>
-      <c r="CE4" t="inlineStr"/>
+      <c r="U4" s="8" t="inlineStr"/>
+      <c r="V4" s="8" t="inlineStr"/>
+      <c r="W4" s="8" t="inlineStr"/>
+      <c r="X4" s="8" t="inlineStr"/>
+      <c r="Y4" s="8" t="inlineStr"/>
+      <c r="Z4" s="8" t="inlineStr"/>
+      <c r="AA4" s="8" t="inlineStr"/>
+      <c r="AB4" s="8" t="inlineStr"/>
+      <c r="AC4" s="8" t="inlineStr"/>
+      <c r="AD4" s="8" t="inlineStr"/>
+      <c r="AE4" s="8" t="inlineStr"/>
+      <c r="AF4" s="8" t="inlineStr"/>
+      <c r="AG4" s="8" t="inlineStr"/>
+      <c r="AH4" s="8" t="inlineStr"/>
+      <c r="AI4" s="8" t="inlineStr"/>
+      <c r="AJ4" s="8" t="inlineStr"/>
+      <c r="AK4" s="8" t="inlineStr"/>
+      <c r="AL4" s="8" t="inlineStr"/>
+      <c r="AM4" s="8" t="inlineStr"/>
+      <c r="AN4" s="8" t="inlineStr"/>
+      <c r="AO4" s="8" t="inlineStr"/>
+      <c r="AP4" s="8" t="inlineStr"/>
+      <c r="AQ4" s="8" t="inlineStr"/>
+      <c r="AR4" s="8" t="inlineStr"/>
+      <c r="AS4" s="8" t="inlineStr"/>
+      <c r="AT4" s="8" t="inlineStr"/>
+      <c r="AU4" s="8" t="inlineStr"/>
+      <c r="AV4" s="8" t="inlineStr"/>
+      <c r="AW4" s="8" t="inlineStr"/>
+      <c r="AX4" s="8" t="inlineStr"/>
+      <c r="AY4" s="8" t="inlineStr"/>
+      <c r="AZ4" s="8" t="inlineStr"/>
+      <c r="BA4" s="8" t="inlineStr"/>
+      <c r="BB4" s="8" t="inlineStr"/>
+      <c r="BC4" s="8" t="inlineStr"/>
+      <c r="BD4" s="8" t="inlineStr"/>
+      <c r="BE4" s="8" t="inlineStr"/>
+      <c r="BF4" s="8" t="inlineStr"/>
+      <c r="BG4" s="8" t="inlineStr"/>
+      <c r="BH4" s="8" t="inlineStr"/>
+      <c r="BI4" s="8" t="inlineStr"/>
+      <c r="BJ4" s="8" t="inlineStr"/>
+      <c r="BK4" s="8" t="inlineStr"/>
+      <c r="BL4" s="8" t="inlineStr"/>
+      <c r="BM4" s="8" t="inlineStr"/>
+      <c r="BN4" s="8" t="inlineStr"/>
+      <c r="BO4" s="8" t="inlineStr"/>
+      <c r="BP4" s="8" t="inlineStr"/>
+      <c r="BQ4" s="8" t="inlineStr"/>
+      <c r="BR4" s="8" t="inlineStr"/>
+      <c r="BS4" s="8" t="inlineStr"/>
+      <c r="BT4" s="8" t="inlineStr"/>
+      <c r="BU4" s="8" t="inlineStr"/>
+      <c r="BV4" s="8" t="inlineStr"/>
+      <c r="BW4" s="8" t="inlineStr"/>
+      <c r="BX4" s="8" t="inlineStr"/>
+      <c r="BY4" s="8" t="inlineStr"/>
+      <c r="BZ4" s="8" t="inlineStr"/>
+      <c r="CA4" s="8" t="inlineStr"/>
+      <c r="CB4" s="8" t="inlineStr"/>
+      <c r="CC4" s="8" t="inlineStr"/>
+      <c r="CD4" s="8" t="inlineStr"/>
+      <c r="CE4" s="8" t="inlineStr"/>
       <c r="XDC4" s="8" t="n"/>
       <c r="XDD4" s="8" t="n"/>
       <c r="XDE4" s="8" t="n"/>
@@ -1430,115 +1430,115 @@
       <c r="V5" s="8" t="n">
         <v>0.67</v>
       </c>
-      <c r="W5" t="inlineStr"/>
+      <c r="W5" s="8" t="inlineStr"/>
       <c r="X5" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="Y5" s="8" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="Z5" t="inlineStr"/>
+      <c r="Z5" s="8" t="inlineStr"/>
       <c r="AA5" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="AB5" s="8" t="n">
         <v>0.59</v>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" s="8" t="inlineStr"/>
       <c r="AD5" s="8" t="n">
         <v>0.66</v>
       </c>
       <c r="AE5" s="8" t="n">
         <v>0.68</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
+      <c r="AF5" s="8" t="inlineStr"/>
       <c r="AG5" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="AH5" s="8" t="n">
         <v>0.49</v>
       </c>
-      <c r="AI5" t="inlineStr"/>
+      <c r="AI5" s="8" t="inlineStr"/>
       <c r="AJ5" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="AK5" s="8" t="n">
         <v>0.42</v>
       </c>
-      <c r="AL5" t="inlineStr"/>
+      <c r="AL5" s="8" t="inlineStr"/>
       <c r="AM5" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="AN5" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="AO5" t="inlineStr"/>
+      <c r="AO5" s="8" t="inlineStr"/>
       <c r="AP5" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="AQ5" s="8" t="n">
         <v>0.43</v>
       </c>
-      <c r="AR5" t="inlineStr"/>
+      <c r="AR5" s="8" t="inlineStr"/>
       <c r="AS5" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="AT5" s="8" t="n">
         <v>0.51</v>
       </c>
-      <c r="AU5" t="inlineStr"/>
+      <c r="AU5" s="8" t="inlineStr"/>
       <c r="AV5" s="8" t="n">
         <v>0.78</v>
       </c>
       <c r="AW5" s="8" t="n">
         <v>0.82</v>
       </c>
-      <c r="AX5" t="inlineStr"/>
+      <c r="AX5" s="8" t="inlineStr"/>
       <c r="AY5" s="8" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="AZ5" s="8" t="n">
         <v>0.84</v>
       </c>
-      <c r="BA5" t="inlineStr"/>
+      <c r="BA5" s="8" t="inlineStr"/>
       <c r="BB5" s="8" t="n">
         <v>0.61</v>
       </c>
       <c r="BC5" s="8" t="n">
         <v>0.55</v>
       </c>
-      <c r="BD5" t="inlineStr"/>
+      <c r="BD5" s="8" t="inlineStr"/>
       <c r="BE5" s="8" t="n">
         <v>0.58</v>
       </c>
       <c r="BF5" s="8" t="n">
         <v>0.62</v>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr"/>
-      <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr"/>
-      <c r="BQ5" t="inlineStr"/>
-      <c r="BR5" t="inlineStr"/>
-      <c r="BS5" t="inlineStr"/>
-      <c r="BT5" t="inlineStr"/>
-      <c r="BU5" t="inlineStr"/>
-      <c r="BV5" t="inlineStr"/>
-      <c r="BW5" t="inlineStr"/>
-      <c r="BX5" t="inlineStr"/>
-      <c r="BY5" t="inlineStr"/>
-      <c r="BZ5" t="inlineStr"/>
-      <c r="CA5" t="inlineStr"/>
-      <c r="CB5" t="inlineStr"/>
-      <c r="CC5" t="inlineStr"/>
-      <c r="CD5" t="inlineStr"/>
-      <c r="CE5" t="inlineStr"/>
+      <c r="BG5" s="8" t="inlineStr"/>
+      <c r="BH5" s="8" t="inlineStr"/>
+      <c r="BI5" s="8" t="inlineStr"/>
+      <c r="BJ5" s="8" t="inlineStr"/>
+      <c r="BK5" s="8" t="inlineStr"/>
+      <c r="BL5" s="8" t="inlineStr"/>
+      <c r="BM5" s="8" t="inlineStr"/>
+      <c r="BN5" s="8" t="inlineStr"/>
+      <c r="BO5" s="8" t="inlineStr"/>
+      <c r="BP5" s="8" t="inlineStr"/>
+      <c r="BQ5" s="8" t="inlineStr"/>
+      <c r="BR5" s="8" t="inlineStr"/>
+      <c r="BS5" s="8" t="inlineStr"/>
+      <c r="BT5" s="8" t="inlineStr"/>
+      <c r="BU5" s="8" t="inlineStr"/>
+      <c r="BV5" s="8" t="inlineStr"/>
+      <c r="BW5" s="8" t="inlineStr"/>
+      <c r="BX5" s="8" t="inlineStr"/>
+      <c r="BY5" s="8" t="inlineStr"/>
+      <c r="BZ5" s="8" t="inlineStr"/>
+      <c r="CA5" s="8" t="inlineStr"/>
+      <c r="CB5" s="8" t="inlineStr"/>
+      <c r="CC5" s="8" t="inlineStr"/>
+      <c r="CD5" s="8" t="inlineStr"/>
+      <c r="CE5" s="8" t="inlineStr"/>
       <c r="XDC5" s="8" t="n"/>
       <c r="XDD5" s="8" t="n"/>
       <c r="XDE5" s="8" t="n"/>
@@ -1737,30 +1737,30 @@
       <c r="BG6" s="8" t="n">
         <v>4.84</v>
       </c>
-      <c r="BH6" t="inlineStr"/>
-      <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
-      <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr"/>
-      <c r="BQ6" t="inlineStr"/>
-      <c r="BR6" t="inlineStr"/>
-      <c r="BS6" t="inlineStr"/>
-      <c r="BT6" t="inlineStr"/>
-      <c r="BU6" t="inlineStr"/>
-      <c r="BV6" t="inlineStr"/>
-      <c r="BW6" t="inlineStr"/>
-      <c r="BX6" t="inlineStr"/>
-      <c r="BY6" t="inlineStr"/>
-      <c r="BZ6" t="inlineStr"/>
-      <c r="CA6" t="inlineStr"/>
-      <c r="CB6" t="inlineStr"/>
-      <c r="CC6" t="inlineStr"/>
-      <c r="CD6" t="inlineStr"/>
-      <c r="CE6" t="inlineStr"/>
+      <c r="BH6" s="8" t="inlineStr"/>
+      <c r="BI6" s="8" t="inlineStr"/>
+      <c r="BJ6" s="8" t="inlineStr"/>
+      <c r="BK6" s="8" t="inlineStr"/>
+      <c r="BL6" s="8" t="inlineStr"/>
+      <c r="BM6" s="8" t="inlineStr"/>
+      <c r="BN6" s="8" t="inlineStr"/>
+      <c r="BO6" s="8" t="inlineStr"/>
+      <c r="BP6" s="8" t="inlineStr"/>
+      <c r="BQ6" s="8" t="inlineStr"/>
+      <c r="BR6" s="8" t="inlineStr"/>
+      <c r="BS6" s="8" t="inlineStr"/>
+      <c r="BT6" s="8" t="inlineStr"/>
+      <c r="BU6" s="8" t="inlineStr"/>
+      <c r="BV6" s="8" t="inlineStr"/>
+      <c r="BW6" s="8" t="inlineStr"/>
+      <c r="BX6" s="8" t="inlineStr"/>
+      <c r="BY6" s="8" t="inlineStr"/>
+      <c r="BZ6" s="8" t="inlineStr"/>
+      <c r="CA6" s="8" t="inlineStr"/>
+      <c r="CB6" s="8" t="inlineStr"/>
+      <c r="CC6" s="8" t="inlineStr"/>
+      <c r="CD6" s="8" t="inlineStr"/>
+      <c r="CE6" s="8" t="inlineStr"/>
       <c r="XDC6" s="8" t="n"/>
       <c r="XDD6" s="8" t="n"/>
       <c r="XDE6" s="8" t="n"/>
@@ -1959,30 +1959,30 @@
       <c r="BG7" s="8" t="n">
         <v>-13.85</v>
       </c>
-      <c r="BH7" t="inlineStr"/>
-      <c r="BI7" t="inlineStr"/>
-      <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="inlineStr"/>
-      <c r="BL7" t="inlineStr"/>
-      <c r="BM7" t="inlineStr"/>
-      <c r="BN7" t="inlineStr"/>
-      <c r="BO7" t="inlineStr"/>
-      <c r="BP7" t="inlineStr"/>
-      <c r="BQ7" t="inlineStr"/>
-      <c r="BR7" t="inlineStr"/>
-      <c r="BS7" t="inlineStr"/>
-      <c r="BT7" t="inlineStr"/>
-      <c r="BU7" t="inlineStr"/>
-      <c r="BV7" t="inlineStr"/>
-      <c r="BW7" t="inlineStr"/>
-      <c r="BX7" t="inlineStr"/>
-      <c r="BY7" t="inlineStr"/>
-      <c r="BZ7" t="inlineStr"/>
-      <c r="CA7" t="inlineStr"/>
-      <c r="CB7" t="inlineStr"/>
-      <c r="CC7" t="inlineStr"/>
-      <c r="CD7" t="inlineStr"/>
-      <c r="CE7" t="inlineStr"/>
+      <c r="BH7" s="8" t="inlineStr"/>
+      <c r="BI7" s="8" t="inlineStr"/>
+      <c r="BJ7" s="8" t="inlineStr"/>
+      <c r="BK7" s="8" t="inlineStr"/>
+      <c r="BL7" s="8" t="inlineStr"/>
+      <c r="BM7" s="8" t="inlineStr"/>
+      <c r="BN7" s="8" t="inlineStr"/>
+      <c r="BO7" s="8" t="inlineStr"/>
+      <c r="BP7" s="8" t="inlineStr"/>
+      <c r="BQ7" s="8" t="inlineStr"/>
+      <c r="BR7" s="8" t="inlineStr"/>
+      <c r="BS7" s="8" t="inlineStr"/>
+      <c r="BT7" s="8" t="inlineStr"/>
+      <c r="BU7" s="8" t="inlineStr"/>
+      <c r="BV7" s="8" t="inlineStr"/>
+      <c r="BW7" s="8" t="inlineStr"/>
+      <c r="BX7" s="8" t="inlineStr"/>
+      <c r="BY7" s="8" t="inlineStr"/>
+      <c r="BZ7" s="8" t="inlineStr"/>
+      <c r="CA7" s="8" t="inlineStr"/>
+      <c r="CB7" s="8" t="inlineStr"/>
+      <c r="CC7" s="8" t="inlineStr"/>
+      <c r="CD7" s="8" t="inlineStr"/>
+      <c r="CE7" s="8" t="inlineStr"/>
       <c r="XDC7" s="8" t="n"/>
       <c r="XDD7" s="8" t="n"/>
       <c r="XDE7" s="8" t="n"/>
@@ -2181,30 +2181,30 @@
       <c r="BG8" s="8" t="n">
         <v>-19.64</v>
       </c>
-      <c r="BH8" t="inlineStr"/>
-      <c r="BI8" t="inlineStr"/>
-      <c r="BJ8" t="inlineStr"/>
-      <c r="BK8" t="inlineStr"/>
-      <c r="BL8" t="inlineStr"/>
-      <c r="BM8" t="inlineStr"/>
-      <c r="BN8" t="inlineStr"/>
-      <c r="BO8" t="inlineStr"/>
-      <c r="BP8" t="inlineStr"/>
-      <c r="BQ8" t="inlineStr"/>
-      <c r="BR8" t="inlineStr"/>
-      <c r="BS8" t="inlineStr"/>
-      <c r="BT8" t="inlineStr"/>
-      <c r="BU8" t="inlineStr"/>
-      <c r="BV8" t="inlineStr"/>
-      <c r="BW8" t="inlineStr"/>
-      <c r="BX8" t="inlineStr"/>
-      <c r="BY8" t="inlineStr"/>
-      <c r="BZ8" t="inlineStr"/>
-      <c r="CA8" t="inlineStr"/>
-      <c r="CB8" t="inlineStr"/>
-      <c r="CC8" t="inlineStr"/>
-      <c r="CD8" t="inlineStr"/>
-      <c r="CE8" t="inlineStr"/>
+      <c r="BH8" s="8" t="inlineStr"/>
+      <c r="BI8" s="8" t="inlineStr"/>
+      <c r="BJ8" s="8" t="inlineStr"/>
+      <c r="BK8" s="8" t="inlineStr"/>
+      <c r="BL8" s="8" t="inlineStr"/>
+      <c r="BM8" s="8" t="inlineStr"/>
+      <c r="BN8" s="8" t="inlineStr"/>
+      <c r="BO8" s="8" t="inlineStr"/>
+      <c r="BP8" s="8" t="inlineStr"/>
+      <c r="BQ8" s="8" t="inlineStr"/>
+      <c r="BR8" s="8" t="inlineStr"/>
+      <c r="BS8" s="8" t="inlineStr"/>
+      <c r="BT8" s="8" t="inlineStr"/>
+      <c r="BU8" s="8" t="inlineStr"/>
+      <c r="BV8" s="8" t="inlineStr"/>
+      <c r="BW8" s="8" t="inlineStr"/>
+      <c r="BX8" s="8" t="inlineStr"/>
+      <c r="BY8" s="8" t="inlineStr"/>
+      <c r="BZ8" s="8" t="inlineStr"/>
+      <c r="CA8" s="8" t="inlineStr"/>
+      <c r="CB8" s="8" t="inlineStr"/>
+      <c r="CC8" s="8" t="inlineStr"/>
+      <c r="CD8" s="8" t="inlineStr"/>
+      <c r="CE8" s="8" t="inlineStr"/>
       <c r="XDC8" s="8" t="n"/>
       <c r="XDD8" s="8" t="n"/>
       <c r="XDE8" s="8" t="n"/>
@@ -2403,30 +2403,30 @@
       <c r="BG9" s="8" t="n">
         <v>-15.56</v>
       </c>
-      <c r="BH9" t="inlineStr"/>
-      <c r="BI9" t="inlineStr"/>
-      <c r="BJ9" t="inlineStr"/>
-      <c r="BK9" t="inlineStr"/>
-      <c r="BL9" t="inlineStr"/>
-      <c r="BM9" t="inlineStr"/>
-      <c r="BN9" t="inlineStr"/>
-      <c r="BO9" t="inlineStr"/>
-      <c r="BP9" t="inlineStr"/>
-      <c r="BQ9" t="inlineStr"/>
-      <c r="BR9" t="inlineStr"/>
-      <c r="BS9" t="inlineStr"/>
-      <c r="BT9" t="inlineStr"/>
-      <c r="BU9" t="inlineStr"/>
-      <c r="BV9" t="inlineStr"/>
-      <c r="BW9" t="inlineStr"/>
-      <c r="BX9" t="inlineStr"/>
-      <c r="BY9" t="inlineStr"/>
-      <c r="BZ9" t="inlineStr"/>
-      <c r="CA9" t="inlineStr"/>
-      <c r="CB9" t="inlineStr"/>
-      <c r="CC9" t="inlineStr"/>
-      <c r="CD9" t="inlineStr"/>
-      <c r="CE9" t="inlineStr"/>
+      <c r="BH9" s="8" t="inlineStr"/>
+      <c r="BI9" s="8" t="inlineStr"/>
+      <c r="BJ9" s="8" t="inlineStr"/>
+      <c r="BK9" s="8" t="inlineStr"/>
+      <c r="BL9" s="8" t="inlineStr"/>
+      <c r="BM9" s="8" t="inlineStr"/>
+      <c r="BN9" s="8" t="inlineStr"/>
+      <c r="BO9" s="8" t="inlineStr"/>
+      <c r="BP9" s="8" t="inlineStr"/>
+      <c r="BQ9" s="8" t="inlineStr"/>
+      <c r="BR9" s="8" t="inlineStr"/>
+      <c r="BS9" s="8" t="inlineStr"/>
+      <c r="BT9" s="8" t="inlineStr"/>
+      <c r="BU9" s="8" t="inlineStr"/>
+      <c r="BV9" s="8" t="inlineStr"/>
+      <c r="BW9" s="8" t="inlineStr"/>
+      <c r="BX9" s="8" t="inlineStr"/>
+      <c r="BY9" s="8" t="inlineStr"/>
+      <c r="BZ9" s="8" t="inlineStr"/>
+      <c r="CA9" s="8" t="inlineStr"/>
+      <c r="CB9" s="8" t="inlineStr"/>
+      <c r="CC9" s="8" t="inlineStr"/>
+      <c r="CD9" s="8" t="inlineStr"/>
+      <c r="CE9" s="8" t="inlineStr"/>
       <c r="XDC9" s="8" t="n"/>
       <c r="XDD9" s="8" t="n"/>
       <c r="XDE9" s="8" t="n"/>
@@ -2625,30 +2625,30 @@
       <c r="BG10" s="8" t="n">
         <v>-23.68</v>
       </c>
-      <c r="BH10" t="inlineStr"/>
-      <c r="BI10" t="inlineStr"/>
-      <c r="BJ10" t="inlineStr"/>
-      <c r="BK10" t="inlineStr"/>
-      <c r="BL10" t="inlineStr"/>
-      <c r="BM10" t="inlineStr"/>
-      <c r="BN10" t="inlineStr"/>
-      <c r="BO10" t="inlineStr"/>
-      <c r="BP10" t="inlineStr"/>
-      <c r="BQ10" t="inlineStr"/>
-      <c r="BR10" t="inlineStr"/>
-      <c r="BS10" t="inlineStr"/>
-      <c r="BT10" t="inlineStr"/>
-      <c r="BU10" t="inlineStr"/>
-      <c r="BV10" t="inlineStr"/>
-      <c r="BW10" t="inlineStr"/>
-      <c r="BX10" t="inlineStr"/>
-      <c r="BY10" t="inlineStr"/>
-      <c r="BZ10" t="inlineStr"/>
-      <c r="CA10" t="inlineStr"/>
-      <c r="CB10" t="inlineStr"/>
-      <c r="CC10" t="inlineStr"/>
-      <c r="CD10" t="inlineStr"/>
-      <c r="CE10" t="inlineStr"/>
+      <c r="BH10" s="8" t="inlineStr"/>
+      <c r="BI10" s="8" t="inlineStr"/>
+      <c r="BJ10" s="8" t="inlineStr"/>
+      <c r="BK10" s="8" t="inlineStr"/>
+      <c r="BL10" s="8" t="inlineStr"/>
+      <c r="BM10" s="8" t="inlineStr"/>
+      <c r="BN10" s="8" t="inlineStr"/>
+      <c r="BO10" s="8" t="inlineStr"/>
+      <c r="BP10" s="8" t="inlineStr"/>
+      <c r="BQ10" s="8" t="inlineStr"/>
+      <c r="BR10" s="8" t="inlineStr"/>
+      <c r="BS10" s="8" t="inlineStr"/>
+      <c r="BT10" s="8" t="inlineStr"/>
+      <c r="BU10" s="8" t="inlineStr"/>
+      <c r="BV10" s="8" t="inlineStr"/>
+      <c r="BW10" s="8" t="inlineStr"/>
+      <c r="BX10" s="8" t="inlineStr"/>
+      <c r="BY10" s="8" t="inlineStr"/>
+      <c r="BZ10" s="8" t="inlineStr"/>
+      <c r="CA10" s="8" t="inlineStr"/>
+      <c r="CB10" s="8" t="inlineStr"/>
+      <c r="CC10" s="8" t="inlineStr"/>
+      <c r="CD10" s="8" t="inlineStr"/>
+      <c r="CE10" s="8" t="inlineStr"/>
       <c r="XDC10" s="8" t="n"/>
       <c r="XDD10" s="8" t="n"/>
       <c r="XDE10" s="8" t="n"/>
@@ -2853,40 +2853,40 @@
       <c r="BI11" s="8" t="n">
         <v>1.51</v>
       </c>
-      <c r="BJ11" t="inlineStr"/>
+      <c r="BJ11" s="8" t="inlineStr"/>
       <c r="BK11" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="BL11" s="8" t="n">
         <v>0.72</v>
       </c>
-      <c r="BM11" t="inlineStr"/>
+      <c r="BM11" s="8" t="inlineStr"/>
       <c r="BN11" s="8" t="n">
         <v>0.6</v>
       </c>
       <c r="BO11" s="8" t="n">
         <v>0.68</v>
       </c>
-      <c r="BP11" t="inlineStr"/>
+      <c r="BP11" s="8" t="inlineStr"/>
       <c r="BQ11" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="BR11" s="8" t="n">
         <v>0.83</v>
       </c>
-      <c r="BS11" t="inlineStr"/>
-      <c r="BT11" t="inlineStr"/>
-      <c r="BU11" t="inlineStr"/>
-      <c r="BV11" t="inlineStr"/>
-      <c r="BW11" t="inlineStr"/>
-      <c r="BX11" t="inlineStr"/>
-      <c r="BY11" t="inlineStr"/>
-      <c r="BZ11" t="inlineStr"/>
-      <c r="CA11" t="inlineStr"/>
-      <c r="CB11" t="inlineStr"/>
-      <c r="CC11" t="inlineStr"/>
-      <c r="CD11" t="inlineStr"/>
-      <c r="CE11" t="inlineStr"/>
+      <c r="BS11" s="8" t="inlineStr"/>
+      <c r="BT11" s="8" t="inlineStr"/>
+      <c r="BU11" s="8" t="inlineStr"/>
+      <c r="BV11" s="8" t="inlineStr"/>
+      <c r="BW11" s="8" t="inlineStr"/>
+      <c r="BX11" s="8" t="inlineStr"/>
+      <c r="BY11" s="8" t="inlineStr"/>
+      <c r="BZ11" s="8" t="inlineStr"/>
+      <c r="CA11" s="8" t="inlineStr"/>
+      <c r="CB11" s="8" t="inlineStr"/>
+      <c r="CC11" s="8" t="inlineStr"/>
+      <c r="CD11" s="8" t="inlineStr"/>
+      <c r="CE11" s="8" t="inlineStr"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="9">
       <c r="A12" s="8" t="n">
@@ -5708,265 +5708,518 @@
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="9">
-      <c r="A23" t="n">
+      <c r="A23" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Sprint_rn_8412</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>19:27:28</t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="8" t="n">
         <v>0.49</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" s="8" t="n">
         <v>0.18</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23" s="8" t="n">
         <v>-5.26</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23" s="8" t="n">
         <v>0.48</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" s="8" t="n">
         <v>0.25</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23" s="8" t="n">
         <v>4.17</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23" s="8" t="n">
         <v>0.53</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M23" s="8" t="n">
         <v>0.27</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N23" s="8" t="n">
         <v>3.85</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O23" s="8" t="n">
         <v>0.75</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P23" s="8" t="n">
         <v>0.38</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q23" s="8" t="n">
         <v>-5</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R23" s="8" t="n">
         <v>0.44</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S23" s="8" t="n">
         <v>0.31</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T23" s="8" t="n">
         <v>-6.06</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U23" s="8" t="n">
         <v>0.67</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V23" s="8" t="n">
         <v>0.35</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W23" s="8" t="n">
         <v>2.94</v>
       </c>
-      <c r="X23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y23" t="n">
+      <c r="X23" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y23" s="8" t="n">
         <v>0.22</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="Z23" s="8" t="n">
         <v>4.76</v>
       </c>
-      <c r="AA23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="AA23" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB23" s="8" t="n">
         <v>0.31</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AC23" s="8" t="n">
         <v>6.9</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AD23" s="8" t="n">
         <v>0.66</v>
       </c>
-      <c r="AE23" t="n">
+      <c r="AE23" s="8" t="n">
         <v>0.37</v>
       </c>
-      <c r="AF23" t="n">
+      <c r="AF23" s="8" t="n">
         <v>5.71</v>
       </c>
-      <c r="AG23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH23" t="n">
+      <c r="AG23" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH23" s="8" t="n">
         <v>0.24</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AI23" s="8" t="n">
         <v>4.35</v>
       </c>
-      <c r="AJ23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK23" t="n">
+      <c r="AJ23" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK23" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="AL23" t="n">
+      <c r="AL23" s="8" t="n">
         <v>5.26</v>
       </c>
-      <c r="AM23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN23" t="n">
+      <c r="AM23" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN23" s="8" t="n">
         <v>0.24</v>
       </c>
-      <c r="AO23" t="n">
+      <c r="AO23" s="8" t="n">
         <v>9.09</v>
       </c>
-      <c r="AP23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AQ23" t="n">
+      <c r="AP23" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ23" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="AR23" t="n">
+      <c r="AR23" s="8" t="n">
         <v>-4.76</v>
       </c>
-      <c r="AS23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AT23" t="n">
+      <c r="AS23" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AT23" s="8" t="n">
         <v>0.26</v>
       </c>
-      <c r="AU23" t="n">
+      <c r="AU23" s="8" t="n">
         <v>-3.7</v>
       </c>
-      <c r="AV23" t="n">
+      <c r="AV23" s="8" t="n">
         <v>0.78</v>
       </c>
-      <c r="AW23" t="n">
+      <c r="AW23" s="8" t="n">
         <v>0.53</v>
       </c>
-      <c r="AX23" t="n">
+      <c r="AX23" s="8" t="n">
         <v>-8.619999999999999</v>
       </c>
-      <c r="AY23" t="n">
+      <c r="AY23" s="8" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="AZ23" t="n">
+      <c r="AZ23" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="BA23" t="n">
+      <c r="BA23" s="8" t="n">
         <v>5.26</v>
       </c>
-      <c r="BB23" t="n">
+      <c r="BB23" s="8" t="n">
         <v>0.61</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BC23" s="8" t="n">
         <v>0.18</v>
       </c>
-      <c r="BD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE23" t="n">
+      <c r="BD23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" s="8" t="n">
         <v>0.58</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BF23" s="8" t="n">
         <v>0.19</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BG23" s="8" t="n">
         <v>5.56</v>
       </c>
-      <c r="BH23" t="n">
+      <c r="BH23" s="8" t="n">
         <v>2</v>
       </c>
       <c r="BI23" s="14" t="n">
         <v>2.38</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BJ23" s="8" t="n">
         <v>-2.06</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BK23" s="8" t="n">
         <v>0.8</v>
       </c>
-      <c r="BL23" t="n">
+      <c r="BL23" s="8" t="n">
         <v>0.7</v>
       </c>
-      <c r="BM23" t="n">
+      <c r="BM23" s="8" t="n">
         <v>-1.41</v>
       </c>
-      <c r="BN23" t="n">
+      <c r="BN23" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="BO23" t="n">
+      <c r="BO23" s="8" t="n">
         <v>0.7</v>
       </c>
-      <c r="BP23" t="n">
+      <c r="BP23" s="8" t="n">
         <v>-5.41</v>
       </c>
-      <c r="BQ23" t="n">
+      <c r="BQ23" s="8" t="n">
         <v>0.8</v>
       </c>
-      <c r="BR23" t="n">
+      <c r="BR23" s="8" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="BS23" t="n">
+      <c r="BS23" s="8" t="n">
         <v>-1.75</v>
       </c>
-      <c r="BT23" t="n">
+      <c r="BT23" s="8" t="n">
         <v>0.48</v>
       </c>
-      <c r="BU23" t="n">
+      <c r="BU23" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="BV23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BX23" t="n">
+      <c r="BV23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW23" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BX23" s="8" t="n">
         <v>0.09</v>
       </c>
-      <c r="BY23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ23" t="n">
+      <c r="BY23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ23" s="8" t="n">
         <v>0.4</v>
       </c>
-      <c r="CA23" t="n">
+      <c r="CA23" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="CB23" t="n">
+      <c r="CB23" s="8" t="n">
         <v>11.11</v>
       </c>
-      <c r="CC23" t="n">
+      <c r="CC23" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="CD23" t="n">
+      <c r="CD23" s="8" t="n">
         <v>0.09</v>
       </c>
-      <c r="CE23" t="n">
+      <c r="CE23" s="8" t="n">
         <v>-10</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="9">
-      <c r="BI24" s="14" t="n"/>
-      <c r="BY24" s="14" t="n"/>
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Sprint_rn_5693</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>18:52:07</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H24" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="T24" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>-3.23</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>-5.41</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>-4.17</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>-3.85</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>-7.55</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>-10</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI24" s="14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>-7.14</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>-10</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BY24" s="14" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="CB24" t="n">
+        <v>-10</v>
+      </c>
+      <c r="CC24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="CD24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="CE24" t="n">
+        <v>11.11</v>
+      </c>
     </row>
     <row r="1048547" ht="12.75" customHeight="1" s="9"/>
     <row r="1048548" ht="12.75" customHeight="1" s="9"/>
